--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q80_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02657583950774655</v>
+        <v>0.01314249915555069</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02657583950774655</v>
+        <v>0.01314249915555069</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00935860698197857</v>
+        <v>0.00663707040437996</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04914863902446246</v>
+        <v>0.02502185613556114</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04914863902446246</v>
+        <v>0.02502185613556114</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008470514666584279</v>
+        <v>0.00833121049435176</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1018580975211282</v>
+        <v>0.05168560276936301</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1018580975211282</v>
+        <v>0.05168560276936301</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01267376715526377</v>
+        <v>0.01658479383972036</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1720999567874387</v>
+        <v>0.08753644359742206</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1720999567874387</v>
+        <v>0.08753644359742206</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01115364234520065</v>
+        <v>0.02745815577922111</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2123848415694116</v>
+        <v>0.1080670855084972</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2123848415694116</v>
+        <v>0.1080670855084972</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01649818469223733</v>
+        <v>0.03426185009731701</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2084228095874973</v>
+        <v>0.1058496178044953</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2084228095874973</v>
+        <v>0.1058496178044953</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01912774988470075</v>
+        <v>0.03272208279252997</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1879340931380104</v>
+        <v>0.09551651364451115</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1879340931380104</v>
+        <v>0.09551651364451115</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01820340521907908</v>
+        <v>0.02801489892963373</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1739611079331002</v>
+        <v>0.08853663344222154</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1739611079331002</v>
+        <v>0.08853663344222154</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01863992142040763</v>
+        <v>0.0258100556567754</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1727588589010212</v>
+        <v>0.08802740177834795</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1727588589010212</v>
+        <v>0.08802740177834795</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02068344522954376</v>
+        <v>0.02440731393578466</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1577452906253257</v>
+        <v>0.08053740179148411</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1577452906253257</v>
+        <v>0.08053740179148411</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02253846458723146</v>
+        <v>0.02303352301054662</v>
       </c>
     </row>
   </sheetData>
